--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,6 +792,1332 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121471768</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1067</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedlavklubba</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Multiclavula mucida</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers.) R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>427361</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6233895</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121471770</v>
+      </c>
+      <c r="B4" t="n">
+        <v>74694</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>427374</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6233887</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121471772</v>
+      </c>
+      <c r="B5" t="n">
+        <v>74694</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>427333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6233880</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121471777</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80252</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ädelkronlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Gyalecta carneola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Hellb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>427506</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6234095</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121471766</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1067</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedlavklubba</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Multiclavula mucida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pers.) R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>427579</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6234107</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121471774</v>
+      </c>
+      <c r="B8" t="n">
+        <v>74696</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>306</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kornig nållav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>427393</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6234010</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121471767</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80239</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>427567</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6234101</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121471778</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80239</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>427497</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6234110</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121471775</v>
+      </c>
+      <c r="B11" t="n">
+        <v>74694</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>427460</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6234072</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121471773</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1067</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedlavklubba</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Multiclavula mucida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pers.) R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>427365</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6233914</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121471769</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1067</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedlavklubba</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Multiclavula mucida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pers.) R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>427370</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6233894</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121471776</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80239</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>427490</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6234105</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121471771</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80575</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1182</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Violettgrå porlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lepra multipuncta</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Turner) Hafellner</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>427366</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6233856</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471768</v>
+        <v>121471778</v>
       </c>
       <c r="B3" t="n">
-        <v>90504</v>
+        <v>80239</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427361</v>
+        <v>427497</v>
       </c>
       <c r="R3" t="n">
-        <v>6233895</v>
+        <v>6234110</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471770</v>
+        <v>121471769</v>
       </c>
       <c r="B4" t="n">
-        <v>74694</v>
+        <v>90504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427374</v>
+        <v>427370</v>
       </c>
       <c r="R4" t="n">
-        <v>6233887</v>
+        <v>6233894</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471772</v>
+        <v>121471771</v>
       </c>
       <c r="B5" t="n">
-        <v>74694</v>
+        <v>80575</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>1182</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427333</v>
+        <v>427366</v>
       </c>
       <c r="R5" t="n">
-        <v>6233880</v>
+        <v>6233856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471777</v>
+        <v>121471770</v>
       </c>
       <c r="B6" t="n">
-        <v>80252</v>
+        <v>74694</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427506</v>
+        <v>427374</v>
       </c>
       <c r="R6" t="n">
-        <v>6234095</v>
+        <v>6233887</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471766</v>
+        <v>121471773</v>
       </c>
       <c r="B7" t="n">
         <v>90504</v>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427579</v>
+        <v>427365</v>
       </c>
       <c r="R7" t="n">
-        <v>6234107</v>
+        <v>6233914</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1509,7 +1509,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471778</v>
+        <v>121471776</v>
       </c>
       <c r="B10" t="n">
         <v>80239</v>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427497</v>
+        <v>427490</v>
       </c>
       <c r="R10" t="n">
-        <v>6234110</v>
+        <v>6234105</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471773</v>
+        <v>121471772</v>
       </c>
       <c r="B12" t="n">
-        <v>90504</v>
+        <v>74694</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,25 +1725,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427365</v>
+        <v>427333</v>
       </c>
       <c r="R12" t="n">
-        <v>6233914</v>
+        <v>6233880</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471769</v>
+        <v>121471768</v>
       </c>
       <c r="B13" t="n">
         <v>90504</v>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427370</v>
+        <v>427361</v>
       </c>
       <c r="R13" t="n">
-        <v>6233894</v>
+        <v>6233895</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471776</v>
+        <v>121471777</v>
       </c>
       <c r="B14" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427490</v>
+        <v>427506</v>
       </c>
       <c r="R14" t="n">
-        <v>6234105</v>
+        <v>6234095</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471771</v>
+        <v>121471766</v>
       </c>
       <c r="B15" t="n">
-        <v>80575</v>
+        <v>90504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1182</v>
+        <v>1067</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427366</v>
+        <v>427579</v>
       </c>
       <c r="R15" t="n">
-        <v>6233856</v>
+        <v>6234107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471778</v>
+        <v>121471774</v>
       </c>
       <c r="B3" t="n">
-        <v>80239</v>
+        <v>74696</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427497</v>
+        <v>427393</v>
       </c>
       <c r="R3" t="n">
-        <v>6234110</v>
+        <v>6234010</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471769</v>
+        <v>121471775</v>
       </c>
       <c r="B4" t="n">
-        <v>90504</v>
+        <v>74694</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427370</v>
+        <v>427460</v>
       </c>
       <c r="R4" t="n">
-        <v>6233894</v>
+        <v>6234072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471771</v>
+        <v>121471778</v>
       </c>
       <c r="B5" t="n">
-        <v>80575</v>
+        <v>80239</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1182</v>
+        <v>230185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427366</v>
+        <v>427497</v>
       </c>
       <c r="R5" t="n">
-        <v>6233856</v>
+        <v>6234110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471770</v>
+        <v>121471777</v>
       </c>
       <c r="B6" t="n">
-        <v>74694</v>
+        <v>80252</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427374</v>
+        <v>427506</v>
       </c>
       <c r="R6" t="n">
-        <v>6233887</v>
+        <v>6234095</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471773</v>
+        <v>121471767</v>
       </c>
       <c r="B7" t="n">
-        <v>90504</v>
+        <v>80239</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427365</v>
+        <v>427567</v>
       </c>
       <c r="R7" t="n">
-        <v>6233914</v>
+        <v>6234101</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471774</v>
+        <v>121471776</v>
       </c>
       <c r="B8" t="n">
-        <v>74696</v>
+        <v>80239</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,21 +1321,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>306</v>
+        <v>230185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427393</v>
+        <v>427490</v>
       </c>
       <c r="R8" t="n">
-        <v>6234010</v>
+        <v>6234105</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471767</v>
+        <v>121471769</v>
       </c>
       <c r="B9" t="n">
-        <v>80239</v>
+        <v>90505</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427567</v>
+        <v>427370</v>
       </c>
       <c r="R9" t="n">
-        <v>6234101</v>
+        <v>6233894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471776</v>
+        <v>121471772</v>
       </c>
       <c r="B10" t="n">
-        <v>80239</v>
+        <v>74694</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427490</v>
+        <v>427333</v>
       </c>
       <c r="R10" t="n">
-        <v>6234105</v>
+        <v>6233880</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471775</v>
+        <v>121471770</v>
       </c>
       <c r="B11" t="n">
         <v>74694</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427460</v>
+        <v>427374</v>
       </c>
       <c r="R11" t="n">
-        <v>6234072</v>
+        <v>6233887</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471772</v>
+        <v>121471766</v>
       </c>
       <c r="B12" t="n">
-        <v>74694</v>
+        <v>90505</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,25 +1725,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427333</v>
+        <v>427579</v>
       </c>
       <c r="R12" t="n">
-        <v>6233880</v>
+        <v>6234107</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471768</v>
+        <v>121471771</v>
       </c>
       <c r="B13" t="n">
-        <v>90504</v>
+        <v>80575</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,25 +1827,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1067</v>
+        <v>1182</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427361</v>
+        <v>427366</v>
       </c>
       <c r="R13" t="n">
-        <v>6233895</v>
+        <v>6233856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471777</v>
+        <v>121471773</v>
       </c>
       <c r="B14" t="n">
-        <v>80252</v>
+        <v>90505</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1933,21 +1933,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1144</v>
+        <v>1067</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427506</v>
+        <v>427365</v>
       </c>
       <c r="R14" t="n">
-        <v>6234095</v>
+        <v>6233914</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471766</v>
+        <v>121471768</v>
       </c>
       <c r="B15" t="n">
-        <v>90504</v>
+        <v>90505</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427579</v>
+        <v>427361</v>
       </c>
       <c r="R15" t="n">
-        <v>6234107</v>
+        <v>6233895</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471774</v>
+        <v>121471773</v>
       </c>
       <c r="B3" t="n">
-        <v>74696</v>
+        <v>90508</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>306</v>
+        <v>1067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427393</v>
+        <v>427365</v>
       </c>
       <c r="R3" t="n">
-        <v>6234010</v>
+        <v>6233914</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471775</v>
+        <v>121471770</v>
       </c>
       <c r="B4" t="n">
-        <v>74694</v>
+        <v>74697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427460</v>
+        <v>427374</v>
       </c>
       <c r="R4" t="n">
-        <v>6234072</v>
+        <v>6233887</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471778</v>
+        <v>121471772</v>
       </c>
       <c r="B5" t="n">
-        <v>80239</v>
+        <v>74697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427497</v>
+        <v>427333</v>
       </c>
       <c r="R5" t="n">
-        <v>6234110</v>
+        <v>6233880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471777</v>
+        <v>121471771</v>
       </c>
       <c r="B6" t="n">
-        <v>80252</v>
+        <v>80578</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1144</v>
+        <v>1182</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427506</v>
+        <v>427366</v>
       </c>
       <c r="R6" t="n">
-        <v>6234095</v>
+        <v>6233856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471767</v>
+        <v>121471774</v>
       </c>
       <c r="B7" t="n">
-        <v>80239</v>
+        <v>74699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427567</v>
+        <v>427393</v>
       </c>
       <c r="R7" t="n">
-        <v>6234101</v>
+        <v>6234010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471776</v>
+        <v>121471775</v>
       </c>
       <c r="B8" t="n">
-        <v>80239</v>
+        <v>74697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,21 +1321,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427490</v>
+        <v>427460</v>
       </c>
       <c r="R8" t="n">
-        <v>6234105</v>
+        <v>6234072</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471769</v>
+        <v>121471776</v>
       </c>
       <c r="B9" t="n">
-        <v>90505</v>
+        <v>80242</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427370</v>
+        <v>427490</v>
       </c>
       <c r="R9" t="n">
-        <v>6233894</v>
+        <v>6234105</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471772</v>
+        <v>121471777</v>
       </c>
       <c r="B10" t="n">
-        <v>74694</v>
+        <v>80255</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,25 +1521,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427333</v>
+        <v>427506</v>
       </c>
       <c r="R10" t="n">
-        <v>6233880</v>
+        <v>6234095</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471770</v>
+        <v>121471766</v>
       </c>
       <c r="B11" t="n">
-        <v>74694</v>
+        <v>90508</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427374</v>
+        <v>427579</v>
       </c>
       <c r="R11" t="n">
-        <v>6233887</v>
+        <v>6234107</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471766</v>
+        <v>121471769</v>
       </c>
       <c r="B12" t="n">
-        <v>90505</v>
+        <v>90508</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427579</v>
+        <v>427370</v>
       </c>
       <c r="R12" t="n">
-        <v>6234107</v>
+        <v>6233894</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471771</v>
+        <v>121471768</v>
       </c>
       <c r="B13" t="n">
-        <v>80575</v>
+        <v>90508</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,25 +1827,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1182</v>
+        <v>1067</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427366</v>
+        <v>427361</v>
       </c>
       <c r="R13" t="n">
-        <v>6233856</v>
+        <v>6233895</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471773</v>
+        <v>121471767</v>
       </c>
       <c r="B14" t="n">
-        <v>90505</v>
+        <v>80242</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427365</v>
+        <v>427567</v>
       </c>
       <c r="R14" t="n">
-        <v>6233914</v>
+        <v>6234101</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471768</v>
+        <v>121471778</v>
       </c>
       <c r="B15" t="n">
-        <v>90505</v>
+        <v>80242</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427361</v>
+        <v>427497</v>
       </c>
       <c r="R15" t="n">
-        <v>6233895</v>
+        <v>6234110</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471773</v>
+        <v>121471770</v>
       </c>
       <c r="B3" t="n">
-        <v>90508</v>
+        <v>74697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427365</v>
+        <v>427374</v>
       </c>
       <c r="R3" t="n">
-        <v>6233914</v>
+        <v>6233887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471770</v>
+        <v>121471777</v>
       </c>
       <c r="B4" t="n">
-        <v>74697</v>
+        <v>80255</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427374</v>
+        <v>427506</v>
       </c>
       <c r="R4" t="n">
-        <v>6233887</v>
+        <v>6234095</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471772</v>
+        <v>121471766</v>
       </c>
       <c r="B5" t="n">
-        <v>74697</v>
+        <v>90508</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427333</v>
+        <v>427579</v>
       </c>
       <c r="R5" t="n">
-        <v>6233880</v>
+        <v>6234107</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471771</v>
+        <v>121471773</v>
       </c>
       <c r="B6" t="n">
-        <v>80578</v>
+        <v>90508</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1182</v>
+        <v>1067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427366</v>
+        <v>427365</v>
       </c>
       <c r="R6" t="n">
-        <v>6233856</v>
+        <v>6233914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471774</v>
+        <v>121471772</v>
       </c>
       <c r="B7" t="n">
-        <v>74699</v>
+        <v>74697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>306</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427393</v>
+        <v>427333</v>
       </c>
       <c r="R7" t="n">
-        <v>6234010</v>
+        <v>6233880</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471775</v>
+        <v>121471771</v>
       </c>
       <c r="B8" t="n">
-        <v>74697</v>
+        <v>80578</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>1182</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427460</v>
+        <v>427366</v>
       </c>
       <c r="R8" t="n">
-        <v>6234072</v>
+        <v>6233856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471776</v>
+        <v>121471778</v>
       </c>
       <c r="B9" t="n">
         <v>80242</v>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427490</v>
+        <v>427497</v>
       </c>
       <c r="R9" t="n">
-        <v>6234105</v>
+        <v>6234110</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471777</v>
+        <v>121471768</v>
       </c>
       <c r="B10" t="n">
-        <v>80255</v>
+        <v>90508</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1144</v>
+        <v>1067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427506</v>
+        <v>427361</v>
       </c>
       <c r="R10" t="n">
-        <v>6234095</v>
+        <v>6233895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471766</v>
+        <v>121471769</v>
       </c>
       <c r="B11" t="n">
         <v>90508</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427579</v>
+        <v>427370</v>
       </c>
       <c r="R11" t="n">
-        <v>6234107</v>
+        <v>6233894</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471769</v>
+        <v>121471775</v>
       </c>
       <c r="B12" t="n">
-        <v>90508</v>
+        <v>74697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,25 +1725,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427370</v>
+        <v>427460</v>
       </c>
       <c r="R12" t="n">
-        <v>6233894</v>
+        <v>6234072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471768</v>
+        <v>121471776</v>
       </c>
       <c r="B13" t="n">
-        <v>90508</v>
+        <v>80242</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,25 +1827,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427361</v>
+        <v>427490</v>
       </c>
       <c r="R13" t="n">
-        <v>6233895</v>
+        <v>6234105</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471778</v>
+        <v>121471774</v>
       </c>
       <c r="B15" t="n">
-        <v>80242</v>
+        <v>74699</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427497</v>
+        <v>427393</v>
       </c>
       <c r="R15" t="n">
-        <v>6234110</v>
+        <v>6234010</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471770</v>
+        <v>121471766</v>
       </c>
       <c r="B3" t="n">
-        <v>74697</v>
+        <v>90514</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427374</v>
+        <v>427579</v>
       </c>
       <c r="R3" t="n">
-        <v>6233887</v>
+        <v>6234107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471777</v>
+        <v>121471772</v>
       </c>
       <c r="B4" t="n">
-        <v>80255</v>
+        <v>74698</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427506</v>
+        <v>427333</v>
       </c>
       <c r="R4" t="n">
-        <v>6234095</v>
+        <v>6233880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471766</v>
+        <v>121471769</v>
       </c>
       <c r="B5" t="n">
-        <v>90508</v>
+        <v>90514</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427579</v>
+        <v>427370</v>
       </c>
       <c r="R5" t="n">
-        <v>6234107</v>
+        <v>6233894</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471773</v>
+        <v>121471771</v>
       </c>
       <c r="B6" t="n">
-        <v>90508</v>
+        <v>80579</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1067</v>
+        <v>1182</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427365</v>
+        <v>427366</v>
       </c>
       <c r="R6" t="n">
-        <v>6233914</v>
+        <v>6233856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471772</v>
+        <v>121471778</v>
       </c>
       <c r="B7" t="n">
-        <v>74697</v>
+        <v>80243</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427333</v>
+        <v>427497</v>
       </c>
       <c r="R7" t="n">
-        <v>6233880</v>
+        <v>6234110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471771</v>
+        <v>121471775</v>
       </c>
       <c r="B8" t="n">
-        <v>80578</v>
+        <v>74698</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1182</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427366</v>
+        <v>427460</v>
       </c>
       <c r="R8" t="n">
-        <v>6233856</v>
+        <v>6234072</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471778</v>
+        <v>121471770</v>
       </c>
       <c r="B9" t="n">
-        <v>80242</v>
+        <v>74698</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427497</v>
+        <v>427374</v>
       </c>
       <c r="R9" t="n">
-        <v>6234110</v>
+        <v>6233887</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471768</v>
+        <v>121471773</v>
       </c>
       <c r="B10" t="n">
-        <v>90508</v>
+        <v>90514</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427361</v>
+        <v>427365</v>
       </c>
       <c r="R10" t="n">
-        <v>6233895</v>
+        <v>6233914</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471769</v>
+        <v>121471767</v>
       </c>
       <c r="B11" t="n">
-        <v>90508</v>
+        <v>80243</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427370</v>
+        <v>427567</v>
       </c>
       <c r="R11" t="n">
-        <v>6233894</v>
+        <v>6234101</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471775</v>
+        <v>121471768</v>
       </c>
       <c r="B12" t="n">
-        <v>74697</v>
+        <v>90514</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,25 +1725,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427460</v>
+        <v>427361</v>
       </c>
       <c r="R12" t="n">
-        <v>6234072</v>
+        <v>6233895</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471776</v>
+        <v>121471777</v>
       </c>
       <c r="B13" t="n">
-        <v>80242</v>
+        <v>80256</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,25 +1827,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427490</v>
+        <v>427506</v>
       </c>
       <c r="R13" t="n">
-        <v>6234105</v>
+        <v>6234095</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471767</v>
+        <v>121471774</v>
       </c>
       <c r="B14" t="n">
-        <v>80242</v>
+        <v>74700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1933,21 +1933,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427567</v>
+        <v>427393</v>
       </c>
       <c r="R14" t="n">
-        <v>6234101</v>
+        <v>6234010</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471774</v>
+        <v>121471776</v>
       </c>
       <c r="B15" t="n">
-        <v>74699</v>
+        <v>80243</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>306</v>
+        <v>230185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427393</v>
+        <v>427490</v>
       </c>
       <c r="R15" t="n">
-        <v>6234010</v>
+        <v>6234105</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471766</v>
+        <v>121471778</v>
       </c>
       <c r="B3" t="n">
-        <v>90514</v>
+        <v>80244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427579</v>
+        <v>427497</v>
       </c>
       <c r="R3" t="n">
-        <v>6234107</v>
+        <v>6234110</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471772</v>
+        <v>121471775</v>
       </c>
       <c r="B4" t="n">
-        <v>74698</v>
+        <v>74699</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427333</v>
+        <v>427460</v>
       </c>
       <c r="R4" t="n">
-        <v>6233880</v>
+        <v>6234072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471769</v>
+        <v>121471767</v>
       </c>
       <c r="B5" t="n">
-        <v>90514</v>
+        <v>80244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427370</v>
+        <v>427567</v>
       </c>
       <c r="R5" t="n">
-        <v>6233894</v>
+        <v>6234101</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471771</v>
+        <v>121471770</v>
       </c>
       <c r="B6" t="n">
-        <v>80579</v>
+        <v>74699</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1182</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427366</v>
+        <v>427374</v>
       </c>
       <c r="R6" t="n">
-        <v>6233856</v>
+        <v>6233887</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471778</v>
+        <v>121471777</v>
       </c>
       <c r="B7" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427497</v>
+        <v>427506</v>
       </c>
       <c r="R7" t="n">
-        <v>6234110</v>
+        <v>6234095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471775</v>
+        <v>121471771</v>
       </c>
       <c r="B8" t="n">
-        <v>74698</v>
+        <v>80580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>1182</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427460</v>
+        <v>427366</v>
       </c>
       <c r="R8" t="n">
-        <v>6234072</v>
+        <v>6233856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471770</v>
+        <v>121471772</v>
       </c>
       <c r="B9" t="n">
-        <v>74698</v>
+        <v>74699</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427374</v>
+        <v>427333</v>
       </c>
       <c r="R9" t="n">
-        <v>6233887</v>
+        <v>6233880</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471773</v>
+        <v>121471769</v>
       </c>
       <c r="B10" t="n">
-        <v>90514</v>
+        <v>90515</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427365</v>
+        <v>427370</v>
       </c>
       <c r="R10" t="n">
-        <v>6233914</v>
+        <v>6233894</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471767</v>
+        <v>121471766</v>
       </c>
       <c r="B11" t="n">
-        <v>80243</v>
+        <v>90515</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427567</v>
+        <v>427579</v>
       </c>
       <c r="R11" t="n">
-        <v>6234101</v>
+        <v>6234107</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1716,7 @@
         <v>121471768</v>
       </c>
       <c r="B12" t="n">
-        <v>90514</v>
+        <v>90515</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471777</v>
+        <v>121471774</v>
       </c>
       <c r="B13" t="n">
-        <v>80256</v>
+        <v>74701</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,25 +1827,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1144</v>
+        <v>306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427506</v>
+        <v>427393</v>
       </c>
       <c r="R13" t="n">
-        <v>6234095</v>
+        <v>6234010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471774</v>
+        <v>121471773</v>
       </c>
       <c r="B14" t="n">
-        <v>74700</v>
+        <v>90515</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>306</v>
+        <v>1067</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427393</v>
+        <v>427365</v>
       </c>
       <c r="R14" t="n">
-        <v>6234010</v>
+        <v>6233914</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2022,7 +2022,7 @@
         <v>121471776</v>
       </c>
       <c r="B15" t="n">
-        <v>80243</v>
+        <v>80244</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471778</v>
+        <v>121471776</v>
       </c>
       <c r="B3" t="n">
         <v>80244</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427497</v>
+        <v>427490</v>
       </c>
       <c r="R3" t="n">
-        <v>6234110</v>
+        <v>6234105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471775</v>
+        <v>121471774</v>
       </c>
       <c r="B4" t="n">
-        <v>74699</v>
+        <v>74701</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427460</v>
+        <v>427393</v>
       </c>
       <c r="R4" t="n">
-        <v>6234072</v>
+        <v>6234010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471767</v>
+        <v>121471770</v>
       </c>
       <c r="B5" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427567</v>
+        <v>427374</v>
       </c>
       <c r="R5" t="n">
-        <v>6234101</v>
+        <v>6233887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471770</v>
+        <v>121471768</v>
       </c>
       <c r="B6" t="n">
-        <v>74699</v>
+        <v>90515</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427374</v>
+        <v>427361</v>
       </c>
       <c r="R6" t="n">
-        <v>6233887</v>
+        <v>6233895</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471777</v>
+        <v>121471778</v>
       </c>
       <c r="B7" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427506</v>
+        <v>427497</v>
       </c>
       <c r="R7" t="n">
-        <v>6234095</v>
+        <v>6234110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471771</v>
+        <v>121471777</v>
       </c>
       <c r="B8" t="n">
-        <v>80580</v>
+        <v>80257</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1182</v>
+        <v>1144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427366</v>
+        <v>427506</v>
       </c>
       <c r="R8" t="n">
-        <v>6233856</v>
+        <v>6234095</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471772</v>
+        <v>121471775</v>
       </c>
       <c r="B9" t="n">
         <v>74699</v>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427333</v>
+        <v>427460</v>
       </c>
       <c r="R9" t="n">
-        <v>6233880</v>
+        <v>6234072</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471769</v>
+        <v>121471772</v>
       </c>
       <c r="B10" t="n">
-        <v>90515</v>
+        <v>74699</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,25 +1521,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427370</v>
+        <v>427333</v>
       </c>
       <c r="R10" t="n">
-        <v>6233894</v>
+        <v>6233880</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471766</v>
+        <v>121471773</v>
       </c>
       <c r="B11" t="n">
         <v>90515</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427579</v>
+        <v>427365</v>
       </c>
       <c r="R11" t="n">
-        <v>6234107</v>
+        <v>6233914</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471768</v>
+        <v>121471766</v>
       </c>
       <c r="B12" t="n">
         <v>90515</v>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427361</v>
+        <v>427579</v>
       </c>
       <c r="R12" t="n">
-        <v>6233895</v>
+        <v>6234107</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471774</v>
+        <v>121471767</v>
       </c>
       <c r="B13" t="n">
-        <v>74701</v>
+        <v>80244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>306</v>
+        <v>230185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427393</v>
+        <v>427567</v>
       </c>
       <c r="R13" t="n">
-        <v>6234010</v>
+        <v>6234101</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471773</v>
+        <v>121471771</v>
       </c>
       <c r="B14" t="n">
-        <v>90515</v>
+        <v>80580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1067</v>
+        <v>1182</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427365</v>
+        <v>427366</v>
       </c>
       <c r="R14" t="n">
-        <v>6233914</v>
+        <v>6233856</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471776</v>
+        <v>121471769</v>
       </c>
       <c r="B15" t="n">
-        <v>80244</v>
+        <v>90515</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427490</v>
+        <v>427370</v>
       </c>
       <c r="R15" t="n">
-        <v>6234105</v>
+        <v>6233894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471776</v>
+        <v>121471770</v>
       </c>
       <c r="B3" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427490</v>
+        <v>427374</v>
       </c>
       <c r="R3" t="n">
-        <v>6234105</v>
+        <v>6233887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471774</v>
+        <v>121471769</v>
       </c>
       <c r="B4" t="n">
-        <v>74701</v>
+        <v>90515</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>306</v>
+        <v>1067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427393</v>
+        <v>427370</v>
       </c>
       <c r="R4" t="n">
-        <v>6234010</v>
+        <v>6233894</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471770</v>
+        <v>121471775</v>
       </c>
       <c r="B5" t="n">
         <v>74699</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427374</v>
+        <v>427460</v>
       </c>
       <c r="R5" t="n">
-        <v>6233887</v>
+        <v>6234072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471768</v>
+        <v>121471777</v>
       </c>
       <c r="B6" t="n">
-        <v>90515</v>
+        <v>80257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1067</v>
+        <v>1144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427361</v>
+        <v>427506</v>
       </c>
       <c r="R6" t="n">
-        <v>6233895</v>
+        <v>6234095</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471778</v>
+        <v>121471772</v>
       </c>
       <c r="B7" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427497</v>
+        <v>427333</v>
       </c>
       <c r="R7" t="n">
-        <v>6234110</v>
+        <v>6233880</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471777</v>
+        <v>121471771</v>
       </c>
       <c r="B8" t="n">
-        <v>80257</v>
+        <v>80580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1144</v>
+        <v>1182</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427506</v>
+        <v>427366</v>
       </c>
       <c r="R8" t="n">
-        <v>6234095</v>
+        <v>6233856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471775</v>
+        <v>121471776</v>
       </c>
       <c r="B9" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427460</v>
+        <v>427490</v>
       </c>
       <c r="R9" t="n">
-        <v>6234072</v>
+        <v>6234105</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471772</v>
+        <v>121471767</v>
       </c>
       <c r="B10" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427333</v>
+        <v>427567</v>
       </c>
       <c r="R10" t="n">
-        <v>6233880</v>
+        <v>6234101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471773</v>
+        <v>121471778</v>
       </c>
       <c r="B11" t="n">
-        <v>90515</v>
+        <v>80244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427365</v>
+        <v>427497</v>
       </c>
       <c r="R11" t="n">
-        <v>6233914</v>
+        <v>6234110</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471767</v>
+        <v>121471774</v>
       </c>
       <c r="B13" t="n">
-        <v>80244</v>
+        <v>74701</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427567</v>
+        <v>427393</v>
       </c>
       <c r="R13" t="n">
-        <v>6234101</v>
+        <v>6234010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471771</v>
+        <v>121471768</v>
       </c>
       <c r="B14" t="n">
-        <v>80580</v>
+        <v>90515</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1182</v>
+        <v>1067</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427366</v>
+        <v>427361</v>
       </c>
       <c r="R14" t="n">
-        <v>6233856</v>
+        <v>6233895</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471769</v>
+        <v>121471773</v>
       </c>
       <c r="B15" t="n">
         <v>90515</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427370</v>
+        <v>427365</v>
       </c>
       <c r="R15" t="n">
-        <v>6233894</v>
+        <v>6233914</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471770</v>
+        <v>121471778</v>
       </c>
       <c r="B3" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427374</v>
+        <v>427497</v>
       </c>
       <c r="R3" t="n">
-        <v>6233887</v>
+        <v>6234110</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471769</v>
+        <v>121471768</v>
       </c>
       <c r="B4" t="n">
         <v>90515</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427370</v>
+        <v>427361</v>
       </c>
       <c r="R4" t="n">
-        <v>6233894</v>
+        <v>6233895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471777</v>
+        <v>121471772</v>
       </c>
       <c r="B6" t="n">
-        <v>80257</v>
+        <v>74699</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427506</v>
+        <v>427333</v>
       </c>
       <c r="R6" t="n">
-        <v>6234095</v>
+        <v>6233880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471772</v>
+        <v>121471777</v>
       </c>
       <c r="B7" t="n">
-        <v>74699</v>
+        <v>80257</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427333</v>
+        <v>427506</v>
       </c>
       <c r="R7" t="n">
-        <v>6233880</v>
+        <v>6234095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471771</v>
+        <v>121471770</v>
       </c>
       <c r="B8" t="n">
-        <v>80580</v>
+        <v>74699</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1182</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427366</v>
+        <v>427374</v>
       </c>
       <c r="R8" t="n">
-        <v>6233856</v>
+        <v>6233887</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471776</v>
+        <v>121471767</v>
       </c>
       <c r="B9" t="n">
         <v>80244</v>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427490</v>
+        <v>427567</v>
       </c>
       <c r="R9" t="n">
-        <v>6234105</v>
+        <v>6234101</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471767</v>
+        <v>121471773</v>
       </c>
       <c r="B10" t="n">
-        <v>80244</v>
+        <v>90515</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,25 +1521,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427567</v>
+        <v>427365</v>
       </c>
       <c r="R10" t="n">
-        <v>6234101</v>
+        <v>6233914</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471778</v>
+        <v>121471771</v>
       </c>
       <c r="B11" t="n">
-        <v>80244</v>
+        <v>80580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230185</v>
+        <v>1182</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427497</v>
+        <v>427366</v>
       </c>
       <c r="R11" t="n">
-        <v>6234110</v>
+        <v>6233856</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471766</v>
+        <v>121471776</v>
       </c>
       <c r="B12" t="n">
-        <v>90515</v>
+        <v>80244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,25 +1725,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427579</v>
+        <v>427490</v>
       </c>
       <c r="R12" t="n">
-        <v>6234107</v>
+        <v>6234105</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471768</v>
+        <v>121471769</v>
       </c>
       <c r="B14" t="n">
         <v>90515</v>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427361</v>
+        <v>427370</v>
       </c>
       <c r="R14" t="n">
-        <v>6233895</v>
+        <v>6233894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471773</v>
+        <v>121471766</v>
       </c>
       <c r="B15" t="n">
         <v>90515</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427365</v>
+        <v>427579</v>
       </c>
       <c r="R15" t="n">
-        <v>6233914</v>
+        <v>6234107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471772</v>
+        <v>121471777</v>
       </c>
       <c r="B6" t="n">
-        <v>74699</v>
+        <v>80257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427333</v>
+        <v>427506</v>
       </c>
       <c r="R6" t="n">
-        <v>6233880</v>
+        <v>6234095</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471777</v>
+        <v>121471772</v>
       </c>
       <c r="B7" t="n">
-        <v>80257</v>
+        <v>74699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427506</v>
+        <v>427333</v>
       </c>
       <c r="R7" t="n">
-        <v>6234095</v>
+        <v>6233880</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471776</v>
+        <v>121471774</v>
       </c>
       <c r="B12" t="n">
-        <v>80244</v>
+        <v>74701</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,21 +1729,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427490</v>
+        <v>427393</v>
       </c>
       <c r="R12" t="n">
-        <v>6234105</v>
+        <v>6234010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471774</v>
+        <v>121471776</v>
       </c>
       <c r="B13" t="n">
-        <v>74701</v>
+        <v>80244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>306</v>
+        <v>230185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427393</v>
+        <v>427490</v>
       </c>
       <c r="R13" t="n">
-        <v>6234010</v>
+        <v>6234105</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471778</v>
+        <v>121471773</v>
       </c>
       <c r="B3" t="n">
-        <v>80244</v>
+        <v>90522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427497</v>
+        <v>427365</v>
       </c>
       <c r="R3" t="n">
-        <v>6234110</v>
+        <v>6233914</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471768</v>
+        <v>121471770</v>
       </c>
       <c r="B4" t="n">
-        <v>90515</v>
+        <v>74706</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427361</v>
+        <v>427374</v>
       </c>
       <c r="R4" t="n">
-        <v>6233895</v>
+        <v>6233887</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471775</v>
+        <v>121471776</v>
       </c>
       <c r="B5" t="n">
-        <v>74699</v>
+        <v>80251</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427460</v>
+        <v>427490</v>
       </c>
       <c r="R5" t="n">
-        <v>6234072</v>
+        <v>6234105</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471777</v>
+        <v>121471769</v>
       </c>
       <c r="B6" t="n">
-        <v>80257</v>
+        <v>90522</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1144</v>
+        <v>1067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427506</v>
+        <v>427370</v>
       </c>
       <c r="R6" t="n">
-        <v>6234095</v>
+        <v>6233894</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471772</v>
+        <v>121471771</v>
       </c>
       <c r="B7" t="n">
-        <v>74699</v>
+        <v>80587</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>1182</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427333</v>
+        <v>427366</v>
       </c>
       <c r="R7" t="n">
-        <v>6233880</v>
+        <v>6233856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471770</v>
+        <v>121471777</v>
       </c>
       <c r="B8" t="n">
-        <v>74699</v>
+        <v>80264</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427374</v>
+        <v>427506</v>
       </c>
       <c r="R8" t="n">
-        <v>6233887</v>
+        <v>6234095</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471767</v>
+        <v>121471766</v>
       </c>
       <c r="B9" t="n">
-        <v>80244</v>
+        <v>90522</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427567</v>
+        <v>427579</v>
       </c>
       <c r="R9" t="n">
-        <v>6234101</v>
+        <v>6234107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471773</v>
+        <v>121471774</v>
       </c>
       <c r="B10" t="n">
-        <v>90515</v>
+        <v>74708</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,25 +1521,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1067</v>
+        <v>306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427365</v>
+        <v>427393</v>
       </c>
       <c r="R10" t="n">
-        <v>6233914</v>
+        <v>6234010</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471771</v>
+        <v>121471767</v>
       </c>
       <c r="B11" t="n">
-        <v>80580</v>
+        <v>80251</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1182</v>
+        <v>230185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427366</v>
+        <v>427567</v>
       </c>
       <c r="R11" t="n">
-        <v>6233856</v>
+        <v>6234101</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471774</v>
+        <v>121471775</v>
       </c>
       <c r="B12" t="n">
-        <v>74701</v>
+        <v>74706</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,21 +1729,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>306</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427393</v>
+        <v>427460</v>
       </c>
       <c r="R12" t="n">
-        <v>6234010</v>
+        <v>6234072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471776</v>
+        <v>121471768</v>
       </c>
       <c r="B13" t="n">
-        <v>80244</v>
+        <v>90522</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,25 +1827,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427490</v>
+        <v>427361</v>
       </c>
       <c r="R13" t="n">
-        <v>6234105</v>
+        <v>6233895</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471769</v>
+        <v>121471772</v>
       </c>
       <c r="B14" t="n">
-        <v>90515</v>
+        <v>74706</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427370</v>
+        <v>427333</v>
       </c>
       <c r="R14" t="n">
-        <v>6233894</v>
+        <v>6233880</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471766</v>
+        <v>121471778</v>
       </c>
       <c r="B15" t="n">
-        <v>90515</v>
+        <v>80251</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427579</v>
+        <v>427497</v>
       </c>
       <c r="R15" t="n">
-        <v>6234107</v>
+        <v>6234110</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471772</v>
+        <v>121471773</v>
       </c>
       <c r="B3" t="n">
-        <v>74706</v>
+        <v>90522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427333</v>
+        <v>427365</v>
       </c>
       <c r="R3" t="n">
-        <v>6233880</v>
+        <v>6233914</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471778</v>
+        <v>121471766</v>
       </c>
       <c r="B4" t="n">
-        <v>80251</v>
+        <v>90522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427497</v>
+        <v>427579</v>
       </c>
       <c r="R4" t="n">
-        <v>6234110</v>
+        <v>6234107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471775</v>
+        <v>121471776</v>
       </c>
       <c r="B5" t="n">
-        <v>74706</v>
+        <v>80251</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427460</v>
+        <v>427490</v>
       </c>
       <c r="R5" t="n">
-        <v>6234072</v>
+        <v>6234105</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471766</v>
+        <v>121471769</v>
       </c>
       <c r="B6" t="n">
         <v>90522</v>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427579</v>
+        <v>427370</v>
       </c>
       <c r="R6" t="n">
-        <v>6234107</v>
+        <v>6233894</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471771</v>
+        <v>121471778</v>
       </c>
       <c r="B7" t="n">
-        <v>80587</v>
+        <v>80251</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1182</v>
+        <v>230185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427366</v>
+        <v>427497</v>
       </c>
       <c r="R7" t="n">
-        <v>6233856</v>
+        <v>6234110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471776</v>
+        <v>121471777</v>
       </c>
       <c r="B8" t="n">
-        <v>80251</v>
+        <v>80264</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427490</v>
+        <v>427506</v>
       </c>
       <c r="R8" t="n">
-        <v>6234105</v>
+        <v>6234095</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471769</v>
+        <v>121471775</v>
       </c>
       <c r="B9" t="n">
-        <v>90522</v>
+        <v>74706</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427370</v>
+        <v>427460</v>
       </c>
       <c r="R9" t="n">
-        <v>6233894</v>
+        <v>6234072</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471773</v>
+        <v>121471774</v>
       </c>
       <c r="B12" t="n">
-        <v>90522</v>
+        <v>74708</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,25 +1725,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1067</v>
+        <v>306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427365</v>
+        <v>427393</v>
       </c>
       <c r="R12" t="n">
-        <v>6233914</v>
+        <v>6234010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471774</v>
+        <v>121471772</v>
       </c>
       <c r="B13" t="n">
-        <v>74708</v>
+        <v>74706</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>306</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427393</v>
+        <v>427333</v>
       </c>
       <c r="R13" t="n">
-        <v>6234010</v>
+        <v>6233880</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471777</v>
+        <v>121471771</v>
       </c>
       <c r="B14" t="n">
-        <v>80264</v>
+        <v>80587</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1144</v>
+        <v>1182</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427506</v>
+        <v>427366</v>
       </c>
       <c r="R14" t="n">
-        <v>6234095</v>
+        <v>6233856</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471778</v>
+        <v>121471777</v>
       </c>
       <c r="B7" t="n">
-        <v>80251</v>
+        <v>80264</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427497</v>
+        <v>427506</v>
       </c>
       <c r="R7" t="n">
-        <v>6234110</v>
+        <v>6234095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471777</v>
+        <v>121471778</v>
       </c>
       <c r="B8" t="n">
-        <v>80264</v>
+        <v>80251</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427506</v>
+        <v>427497</v>
       </c>
       <c r="R8" t="n">
-        <v>6234095</v>
+        <v>6234110</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471773</v>
+        <v>121471772</v>
       </c>
       <c r="B3" t="n">
-        <v>90522</v>
+        <v>74706</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427365</v>
+        <v>427333</v>
       </c>
       <c r="R3" t="n">
-        <v>6233914</v>
+        <v>6233880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471766</v>
+        <v>121471768</v>
       </c>
       <c r="B4" t="n">
         <v>90522</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427579</v>
+        <v>427361</v>
       </c>
       <c r="R4" t="n">
-        <v>6234107</v>
+        <v>6233895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471776</v>
+        <v>121471775</v>
       </c>
       <c r="B5" t="n">
-        <v>80251</v>
+        <v>74706</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427490</v>
+        <v>427460</v>
       </c>
       <c r="R5" t="n">
-        <v>6234105</v>
+        <v>6234072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471769</v>
+        <v>121471778</v>
       </c>
       <c r="B6" t="n">
-        <v>90522</v>
+        <v>80251</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427370</v>
+        <v>427497</v>
       </c>
       <c r="R6" t="n">
-        <v>6233894</v>
+        <v>6234110</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471777</v>
+        <v>121471774</v>
       </c>
       <c r="B7" t="n">
-        <v>80264</v>
+        <v>74708</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1144</v>
+        <v>306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427506</v>
+        <v>427393</v>
       </c>
       <c r="R7" t="n">
-        <v>6234095</v>
+        <v>6234010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471778</v>
+        <v>121471767</v>
       </c>
       <c r="B8" t="n">
         <v>80251</v>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427497</v>
+        <v>427567</v>
       </c>
       <c r="R8" t="n">
-        <v>6234110</v>
+        <v>6234101</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471775</v>
+        <v>121471769</v>
       </c>
       <c r="B9" t="n">
-        <v>74706</v>
+        <v>90522</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427460</v>
+        <v>427370</v>
       </c>
       <c r="R9" t="n">
-        <v>6234072</v>
+        <v>6233894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471770</v>
+        <v>121471773</v>
       </c>
       <c r="B10" t="n">
-        <v>74706</v>
+        <v>90522</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,25 +1521,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427374</v>
+        <v>427365</v>
       </c>
       <c r="R10" t="n">
-        <v>6233887</v>
+        <v>6233914</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471767</v>
+        <v>121471776</v>
       </c>
       <c r="B11" t="n">
         <v>80251</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427567</v>
+        <v>427490</v>
       </c>
       <c r="R11" t="n">
-        <v>6234101</v>
+        <v>6234105</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471774</v>
+        <v>121471777</v>
       </c>
       <c r="B12" t="n">
-        <v>74708</v>
+        <v>80264</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,25 +1725,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>306</v>
+        <v>1144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427393</v>
+        <v>427506</v>
       </c>
       <c r="R12" t="n">
-        <v>6234010</v>
+        <v>6234095</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471772</v>
+        <v>121471770</v>
       </c>
       <c r="B13" t="n">
         <v>74706</v>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427333</v>
+        <v>427374</v>
       </c>
       <c r="R13" t="n">
-        <v>6233880</v>
+        <v>6233887</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471771</v>
+        <v>121471766</v>
       </c>
       <c r="B14" t="n">
-        <v>80587</v>
+        <v>90522</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1182</v>
+        <v>1067</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427366</v>
+        <v>427579</v>
       </c>
       <c r="R14" t="n">
-        <v>6233856</v>
+        <v>6234107</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471768</v>
+        <v>121471771</v>
       </c>
       <c r="B15" t="n">
-        <v>90522</v>
+        <v>80587</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1067</v>
+        <v>1182</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427361</v>
+        <v>427366</v>
       </c>
       <c r="R15" t="n">
-        <v>6233895</v>
+        <v>6233856</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,70 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117228405</v>
+        <v>121471732</v>
       </c>
       <c r="B2" t="n">
-        <v>56260</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100088</v>
+        <v>94</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Puderfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Arthonia cinereopruinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>Schaer.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SÖ Märkesröret, Sk</t>
+          <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>427435</v>
+        <v>427401</v>
       </c>
       <c r="R2" t="n">
-        <v>6234016</v>
+        <v>6234079</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alex Regnér</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Appeltofft, Alex Regnér</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471772</v>
+        <v>121471737</v>
       </c>
       <c r="B3" t="n">
-        <v>74706</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427333</v>
+        <v>427296</v>
       </c>
       <c r="R3" t="n">
-        <v>6233880</v>
+        <v>6233907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471768</v>
+        <v>121471774</v>
       </c>
       <c r="B4" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1067</v>
+        <v>306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427361</v>
+        <v>427393</v>
       </c>
       <c r="R4" t="n">
-        <v>6233895</v>
+        <v>6234010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471775</v>
+        <v>121471766</v>
       </c>
       <c r="B5" t="n">
-        <v>74706</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427460</v>
+        <v>427579</v>
       </c>
       <c r="R5" t="n">
-        <v>6234072</v>
+        <v>6234107</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471778</v>
+        <v>121471768</v>
       </c>
       <c r="B6" t="n">
-        <v>80251</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427497</v>
+        <v>427361</v>
       </c>
       <c r="R6" t="n">
-        <v>6234110</v>
+        <v>6233895</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471774</v>
+        <v>121471769</v>
       </c>
       <c r="B7" t="n">
-        <v>74708</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>306</v>
+        <v>1067</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427393</v>
+        <v>427370</v>
       </c>
       <c r="R7" t="n">
-        <v>6234010</v>
+        <v>6233894</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471767</v>
+        <v>121471773</v>
       </c>
       <c r="B8" t="n">
-        <v>80251</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427567</v>
+        <v>427365</v>
       </c>
       <c r="R8" t="n">
-        <v>6234101</v>
+        <v>6233914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471769</v>
+        <v>121471777</v>
       </c>
       <c r="B9" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1067</v>
+        <v>1144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427370</v>
+        <v>427506</v>
       </c>
       <c r="R9" t="n">
-        <v>6233894</v>
+        <v>6234095</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471773</v>
+        <v>121471771</v>
       </c>
       <c r="B10" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1067</v>
+        <v>1182</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427365</v>
+        <v>427366</v>
       </c>
       <c r="R10" t="n">
-        <v>6233914</v>
+        <v>6233856</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471776</v>
+        <v>121471738</v>
       </c>
       <c r="B11" t="n">
-        <v>80251</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1627,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427490</v>
+        <v>427453</v>
       </c>
       <c r="R11" t="n">
-        <v>6234105</v>
+        <v>6233907</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1681,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471777</v>
+        <v>121471711</v>
       </c>
       <c r="B12" t="n">
-        <v>80264</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427506</v>
+        <v>427414</v>
       </c>
       <c r="R12" t="n">
-        <v>6234095</v>
+        <v>6233832</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1818,12 +1745,7 @@
         <v>121471770</v>
       </c>
       <c r="B13" t="n">
-        <v>74706</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471766</v>
+        <v>121471772</v>
       </c>
       <c r="B14" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427579</v>
+        <v>427333</v>
       </c>
       <c r="R14" t="n">
-        <v>6234107</v>
+        <v>6233880</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471771</v>
+        <v>121471775</v>
       </c>
       <c r="B15" t="n">
-        <v>80587</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1182</v>
+        <v>6439</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427366</v>
+        <v>427460</v>
       </c>
       <c r="R15" t="n">
-        <v>6233856</v>
+        <v>6234072</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,6 +2030,897 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>117228405</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SÖ Märkesröret, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>427435</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6234016</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alex Regnér, Per Appeltofft</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121471733</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>427391</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6234073</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121471736</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>427290</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6233920</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121471740</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>427473</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6233917</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121471741</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>427479</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6233917</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121471742</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>427478</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6233926</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121471767</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>427567</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6234101</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121471776</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>427490</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6234105</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121471778</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>427497</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6234110</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18969-2024 artfynd.xlsx
+++ b/artfynd/A 18969-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471732</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471737</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471774</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471766</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471768</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471769</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471773</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471777</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471771</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471738</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471711</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471770</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471772</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471775</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2145,6 +2220,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117228405</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2242,6 +2322,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471733</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2339,6 +2424,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471736</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471740</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2533,6 +2628,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471741</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2630,6 +2730,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471742</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2727,6 +2832,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471767</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2824,6 +2934,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471776</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2921,8 +3036,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471778</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>